--- a/data/excel/billing_data.xlsx
+++ b/data/excel/billing_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mshrinivasan\BillingAutomation_SLUPius\data\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4421566B-AFFA-422E-B20C-4453EDA659C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79BCEA82-6010-4D23-AFF0-1042E6C3D798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10414,8 +10414,8 @@
       <c r="K146" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="L146" s="35" t="s">
-        <v>554</v>
+      <c r="L146" s="36" t="s">
+        <v>25</v>
       </c>
       <c r="M146" s="36"/>
       <c r="N146" s="36"/>
@@ -10566,7 +10566,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K150:K1048576 J142:J1048576 G135:G1048576 L146" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K150:K1048576 J142:J1048576 G135:G1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>18264</formula1>
       <formula2>49674</formula2>
     </dataValidation>
